--- a/data/trans_orig/P36BPD05_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023</t>
+          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54842</t>
+          <t>54169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>94529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>44785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73278</t>
+          <t>71100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107522</t>
+          <t>108271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154741</t>
+          <t>158663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216021</t>
+          <t>216914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256601</t>
+          <t>257274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216357</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244605</t>
+          <t>244850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446336</t>
+          <t>442414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>493555</t>
+          <t>492806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174967</t>
+          <t>174487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233316</t>
+          <t>232551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155103</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192849</t>
+          <t>193970</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339485</t>
+          <t>343519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415737</t>
+          <t>413547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283798</t>
+          <t>284563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342147</t>
+          <t>342627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321378</t>
+          <t>320257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359124</t>
+          <t>357572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>615604</t>
+          <t>617794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691856</t>
+          <t>687822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>67908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52019</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76853</t>
+          <t>76888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100327</t>
+          <t>100074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137839</t>
+          <t>137258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245358</t>
+          <t>245929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272262</t>
+          <t>272029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267763</t>
+          <t>267728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>292597</t>
+          <t>292743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>520614</t>
+          <t>521195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558126</t>
+          <t>558379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51097</t>
+          <t>51567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87496</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251580</t>
+          <t>256017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125098</t>
+          <t>126908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349861</t>
+          <t>353908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>222878</t>
+          <t>223520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259277</t>
+          <t>258807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223723</t>
+          <t>219286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416340</t>
+          <t>416716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435815</t>
+          <t>431768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>660578</t>
+          <t>658768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35351</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>54474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68599</t>
+          <t>68886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93648</t>
+          <t>94295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123678</t>
+          <t>124268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143391</t>
+          <t>143692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163407</t>
+          <t>163811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177725</t>
+          <t>178603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293368</t>
+          <t>292721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318417</t>
+          <t>318130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40458</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33527</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42670</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>67947</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228787</t>
+          <t>229047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248112</t>
+          <t>247782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222581</t>
+          <t>223688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238590</t>
+          <t>238892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459001</t>
+          <t>457406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482683</t>
+          <t>482902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108451</t>
+          <t>111180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>164673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>323713</t>
+          <t>323714</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147978</t>
+          <t>146510</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>630238</t>
+          <t>573567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281001</t>
+          <t>279496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>834851</t>
+          <t>823459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>459174</t>
+          <t>458577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>514799</t>
+          <t>512070</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217167</t>
+          <t>273839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>699427</t>
+          <t>700896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635804</t>
+          <t>647196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1189654</t>
+          <t>1191159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847405</t>
+          <t>847406</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847405</t>
+          <t>847406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847405</t>
+          <t>847406</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>561207</t>
+          <t>560477</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>817526</t>
+          <t>806143</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>366521</t>
+          <t>369357</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>412477</t>
+          <t>416477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>941511</t>
+          <t>943132</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1288274</t>
+          <t>1306517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>110278</t>
+          <t>121661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>366597</t>
+          <t>367327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>304623</t>
+          <t>300623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>350579</t>
+          <t>347743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>356630</t>
+          <t>338387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>703393</t>
+          <t>701772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1084725</t>
+          <t>1085184</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1769508</t>
+          <t>1775515</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1001414</t>
+          <t>1012666</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1635317</t>
+          <t>1655036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2149513</t>
+          <t>2172576</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3110770</t>
+          <t>3117474</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1682301</t>
+          <t>1676294</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2367084</t>
+          <t>2366625</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2017350</t>
+          <t>1997631</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2651253</t>
+          <t>2640001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3993707</t>
+          <t>3987003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4954964</t>
+          <t>4931901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD05_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54169</t>
+          <t>60277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94529</t>
+          <t>92286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55783</t>
+          <t>65447</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>54161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71100</t>
+          <t>79690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>129769</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>120777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158663</t>
+          <t>162091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>237457</t>
+          <t>244468</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216914</t>
+          <t>226559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257274</t>
+          <t>258568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>233852</t>
+          <t>250614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>236371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244850</t>
+          <t>261900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>471308</t>
+          <t>495083</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442414</t>
+          <t>472815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>492806</t>
+          <t>514129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202242</t>
+          <t>205207</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174487</t>
+          <t>176331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232551</t>
+          <t>235055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>174368</t>
+          <t>182698</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156655</t>
+          <t>161557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>193970</t>
+          <t>203683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>376610</t>
+          <t>387905</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>343519</t>
+          <t>353164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>413547</t>
+          <t>425629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>314872</t>
+          <t>324154</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284563</t>
+          <t>294306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342627</t>
+          <t>353030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>339859</t>
+          <t>363081</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320257</t>
+          <t>342096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357572</t>
+          <t>384222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>654731</t>
+          <t>687235</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617794</t>
+          <t>649511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>687822</t>
+          <t>721976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514227</t>
+          <t>545779</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514227</t>
+          <t>545779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514227</t>
+          <t>545779</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031341</t>
+          <t>1075140</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031341</t>
+          <t>1075140</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031341</t>
+          <t>1075140</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53932</t>
+          <t>54378</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67908</t>
+          <t>68474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>66662</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51873</t>
+          <t>54219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76888</t>
+          <t>79377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>118111</t>
+          <t>121040</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100074</t>
+          <t>104009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137258</t>
+          <t>140452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>259905</t>
+          <t>259475</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245929</t>
+          <t>245379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272029</t>
+          <t>271805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>280437</t>
+          <t>284629</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267728</t>
+          <t>271914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>292743</t>
+          <t>297072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>540342</t>
+          <t>544104</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>521195</t>
+          <t>524692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558379</t>
+          <t>561135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>313837</t>
+          <t>313853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313837</t>
+          <t>313853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313837</t>
+          <t>313853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>344616</t>
+          <t>351291</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344616</t>
+          <t>351291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>344616</t>
+          <t>351291</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>658453</t>
+          <t>665144</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>658453</t>
+          <t>665144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>658453</t>
+          <t>665144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67040</t>
+          <t>76994</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51567</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86854</t>
+          <t>100794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125074</t>
+          <t>64396</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58587</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256017</t>
+          <t>82061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>192114</t>
+          <t>141390</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126908</t>
+          <t>116791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353908</t>
+          <t>169307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>243334</t>
+          <t>293698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223520</t>
+          <t>269898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258807</t>
+          <t>312723</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>350229</t>
+          <t>357089</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219286</t>
+          <t>339424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416716</t>
+          <t>369388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>593562</t>
+          <t>650787</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431768</t>
+          <t>622870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>658768</t>
+          <t>675386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310374</t>
+          <t>370692</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310374</t>
+          <t>370692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310374</t>
+          <t>370692</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475303</t>
+          <t>421485</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475303</t>
+          <t>421485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475303</t>
+          <t>421485</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>785676</t>
+          <t>792177</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>785676</t>
+          <t>792177</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>785676</t>
+          <t>792177</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>48630</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>39159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>42243</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29671</t>
+          <t>34210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44463</t>
+          <t>51741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>80773</t>
+          <t>90873</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>77167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>104884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134685</t>
+          <t>157035</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124268</t>
+          <t>146356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143692</t>
+          <t>166506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>171557</t>
+          <t>184580</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163811</t>
+          <t>175082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178603</t>
+          <t>192613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>306243</t>
+          <t>341615</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292721</t>
+          <t>327604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318130</t>
+          <t>355321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54048</t>
+          <t>53689</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42451</t>
+          <t>42824</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239461</t>
+          <t>240846</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229047</t>
+          <t>229531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247782</t>
+          <t>249362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>231844</t>
+          <t>238525</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223688</t>
+          <t>230064</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238892</t>
+          <t>245143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>471305</t>
+          <t>479372</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>457406</t>
+          <t>466442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482902</t>
+          <t>490237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269245</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269245</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269245</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256108</t>
+          <t>262773</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256108</t>
+          <t>262773</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256108</t>
+          <t>262773</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525353</t>
+          <t>533061</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525353</t>
+          <t>533061</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525353</t>
+          <t>533061</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>135146</t>
+          <t>158893</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111180</t>
+          <t>132805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164673</t>
+          <t>188141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>323714</t>
+          <t>137563</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146510</t>
+          <t>116948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>573567</t>
+          <t>161355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>458859</t>
+          <t>296456</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279496</t>
+          <t>264722</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>823459</t>
+          <t>329948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>488104</t>
+          <t>559712</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>458577</t>
+          <t>530464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>512070</t>
+          <t>585800</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>523692</t>
+          <t>632444</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273839</t>
+          <t>608652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>700896</t>
+          <t>653059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1011796</t>
+          <t>1192156</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>647196</t>
+          <t>1158664</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1191159</t>
+          <t>1223890</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847406</t>
+          <t>770007</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847406</t>
+          <t>770007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847406</t>
+          <t>770007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470655</t>
+          <t>1488612</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470655</t>
+          <t>1488612</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470655</t>
+          <t>1488612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>664994</t>
+          <t>488028</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>560477</t>
+          <t>455706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>806143</t>
+          <t>516997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>390582</t>
+          <t>454247</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>369357</t>
+          <t>430285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>416477</t>
+          <t>477908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1055576</t>
+          <t>942274</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>943132</t>
+          <t>902455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1306517</t>
+          <t>983942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>262810</t>
+          <t>309005</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>280036</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>367327</t>
+          <t>341327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>326518</t>
+          <t>376358</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>300623</t>
+          <t>352697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>347743</t>
+          <t>400320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>589328</t>
+          <t>685363</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338387</t>
+          <t>643695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>701772</t>
+          <t>725182</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927804</t>
+          <t>797033</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927804</t>
+          <t>797033</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927804</t>
+          <t>797033</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717100</t>
+          <t>830605</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717100</t>
+          <t>830605</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717100</t>
+          <t>830605</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644904</t>
+          <t>1627637</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644904</t>
+          <t>1627637</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644904</t>
+          <t>1627637</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1271181</t>
+          <t>1135946</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1085184</t>
+          <t>1071950</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1775515</t>
+          <t>1202254</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1194680</t>
+          <t>1037504</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1012666</t>
+          <t>989836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1655036</t>
+          <t>1087056</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2465861</t>
+          <t>2173450</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2172576</t>
+          <t>2091863</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3117474</t>
+          <t>2250672</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2180628</t>
+          <t>2388395</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1676294</t>
+          <t>2322087</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2366625</t>
+          <t>2452391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2457987</t>
+          <t>2687320</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1997631</t>
+          <t>2637768</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2640001</t>
+          <t>2734988</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4638616</t>
+          <t>5075715</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3987003</t>
+          <t>4998493</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4931901</t>
+          <t>5157302</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
